--- a/Data/Fiscal Data/BTr-Monthly-Debt-Stock-2009-to-current.xlsx
+++ b/Data/Fiscal Data/BTr-Monthly-Debt-Stock-2009-to-current.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AJ\GitHub Repositories\PH-Econ-Data\Data\Fiscal Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF95149-D7F0-455C-BB39-9AC48B9FE589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D45AB8-84A9-4AB2-9AC7-A146BF34F1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="4095" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="18" r:id="rId1"/>
@@ -1194,27 +1194,27 @@
       <c r="G8" s="81"/>
       <c r="H8" s="16">
         <f>+H10+H37</f>
-        <v>18479047</v>
+        <v>18479047.219999999</v>
       </c>
       <c r="I8" s="16">
         <f>+I10+I37</f>
-        <v>18539680</v>
+        <v>18539680.300000001</v>
       </c>
       <c r="J8" s="16">
         <f>+J10+J37</f>
-        <v>18869540</v>
+        <v>18869540.300000001</v>
       </c>
       <c r="K8" s="16">
         <f>+K10+K37</f>
-        <v>0</v>
+        <v>18853820.300000001</v>
       </c>
       <c r="L8" s="16">
         <f>+L10+L37</f>
-        <v>0</v>
+        <v>18990213.300000001</v>
       </c>
       <c r="M8" s="16">
         <f t="shared" ref="M8:S8" si="0">+M10+M37</f>
-        <v>0</v>
+        <v>19370764.300000001</v>
       </c>
       <c r="N8" s="16">
         <f t="shared" si="0"/>
@@ -1266,27 +1266,27 @@
       <c r="G10" s="82"/>
       <c r="H10" s="17">
         <f>+H12+H27</f>
-        <v>18133963</v>
+        <v>18133962.57</v>
       </c>
       <c r="I10" s="17">
         <f>+I12+I27</f>
-        <v>18159698</v>
+        <v>18159698.300000001</v>
       </c>
       <c r="J10" s="17">
         <f>+J12+J27</f>
-        <v>18488134</v>
+        <v>18488134.300000001</v>
       </c>
       <c r="K10" s="17">
         <f>+K12+K27</f>
-        <v>0</v>
+        <v>18470595.300000001</v>
       </c>
       <c r="L10" s="17">
         <f>+L12+L27</f>
-        <v>0</v>
+        <v>18546711.300000001</v>
       </c>
       <c r="M10" s="17">
         <f t="shared" ref="M10:S10" si="1">+M12+M27</f>
-        <v>0</v>
+        <v>19065689.300000001</v>
       </c>
       <c r="N10" s="17">
         <f t="shared" si="1"/>
@@ -1343,27 +1343,27 @@
       <c r="G12" s="19"/>
       <c r="H12" s="20">
         <f>+H13+H25</f>
-        <v>12324775</v>
+        <v>12324774.57</v>
       </c>
       <c r="I12" s="20">
         <f>+I13+I25</f>
-        <v>12479162</v>
+        <v>12479162.300000001</v>
       </c>
       <c r="J12" s="20">
         <f>+J13+J25</f>
-        <v>12534566</v>
+        <v>12534566.300000001</v>
       </c>
       <c r="K12" s="20">
         <f>+K13+K25</f>
-        <v>0</v>
+        <v>12415390.300000001</v>
       </c>
       <c r="L12" s="20">
         <f>+L13+L25</f>
-        <v>0</v>
+        <v>12495513.300000001</v>
       </c>
       <c r="M12" s="20">
         <f t="shared" ref="M12:S12" si="2">+M13+M25</f>
-        <v>0</v>
+        <v>12837836.300000001</v>
       </c>
       <c r="N12" s="20">
         <f t="shared" si="2"/>
@@ -1412,15 +1412,15 @@
       </c>
       <c r="K13" s="20">
         <f>K14+K19</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="L13" s="20">
         <f>L14+L19</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M13" s="20">
         <f t="shared" ref="M13:S13" si="3">M14+M19</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N13" s="20">
         <f t="shared" si="3"/>
@@ -1469,15 +1469,15 @@
       </c>
       <c r="K14" s="22">
         <f>K15+K18</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="L14" s="22">
         <f>L15+L18</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M14" s="22">
         <f t="shared" ref="M14:S14" si="4">M15+M18</f>
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N14" s="22">
         <f t="shared" si="4"/>
@@ -1521,9 +1521,15 @@
       <c r="J15" s="23">
         <v>156</v>
       </c>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
+      <c r="K15" s="23">
+        <v>156</v>
+      </c>
+      <c r="L15" s="23">
+        <v>156</v>
+      </c>
+      <c r="M15" s="23">
+        <v>156</v>
+      </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
@@ -1548,9 +1554,15 @@
       <c r="J16" s="23">
         <v>156</v>
       </c>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="K16" s="23">
+        <v>156</v>
+      </c>
+      <c r="L16" s="23">
+        <v>156</v>
+      </c>
+      <c r="M16" s="23">
+        <v>156</v>
+      </c>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
@@ -1575,9 +1587,15 @@
       <c r="J17" s="23">
         <v>0</v>
       </c>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
+      <c r="K17" s="23">
+        <v>0</v>
+      </c>
+      <c r="L17" s="23">
+        <v>0</v>
+      </c>
+      <c r="M17" s="23">
+        <v>0</v>
+      </c>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
@@ -1602,9 +1620,15 @@
       <c r="J18" s="23">
         <v>0</v>
       </c>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
+      <c r="K18" s="23">
+        <v>0</v>
+      </c>
+      <c r="L18" s="23">
+        <v>0</v>
+      </c>
+      <c r="M18" s="23">
+        <v>0</v>
+      </c>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
@@ -1629,9 +1653,15 @@
       <c r="J19" s="22">
         <v>0</v>
       </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
+      <c r="K19" s="22">
+        <v>0</v>
+      </c>
+      <c r="L19" s="22">
+        <v>0</v>
+      </c>
+      <c r="M19" s="22">
+        <v>0</v>
+      </c>
       <c r="N19" s="22"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
@@ -1771,17 +1801,23 @@
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
       <c r="H25" s="25">
-        <v>12324619</v>
+        <v>12324618.57</v>
       </c>
       <c r="I25" s="25">
-        <v>12479006</v>
+        <v>12479006.300000001</v>
       </c>
       <c r="J25" s="25">
-        <v>12534410</v>
-      </c>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
+        <v>12534410.300000001</v>
+      </c>
+      <c r="K25" s="25">
+        <v>12415234.300000001</v>
+      </c>
+      <c r="L25" s="25">
+        <v>12495357.300000001</v>
+      </c>
+      <c r="M25" s="25">
+        <v>12837680.300000001</v>
+      </c>
       <c r="N25" s="25"/>
       <c r="O25" s="25"/>
       <c r="P25" s="25"/>
@@ -1830,15 +1866,15 @@
       </c>
       <c r="K27" s="20">
         <f>K28+K34</f>
-        <v>0</v>
+        <v>6055205</v>
       </c>
       <c r="L27" s="20">
         <f>L28+L34</f>
-        <v>0</v>
+        <v>6051198</v>
       </c>
       <c r="M27" s="20">
         <f t="shared" ref="M27:S27" si="5">M28+M34</f>
-        <v>0</v>
+        <v>6227853</v>
       </c>
       <c r="N27" s="20">
         <f t="shared" si="5"/>
@@ -1887,15 +1923,15 @@
       </c>
       <c r="K28" s="22">
         <f>K29+K32</f>
-        <v>0</v>
+        <v>2998755</v>
       </c>
       <c r="L28" s="22">
         <f>L29+L32</f>
-        <v>0</v>
+        <v>2999465</v>
       </c>
       <c r="M28" s="22">
         <f t="shared" ref="M28:S28" si="6">M29+M32</f>
-        <v>0</v>
+        <v>3039936</v>
       </c>
       <c r="N28" s="22">
         <f t="shared" si="6"/>
@@ -1944,15 +1980,15 @@
       </c>
       <c r="K29" s="26">
         <f>+K30+K31</f>
-        <v>0</v>
+        <v>2998755</v>
       </c>
       <c r="L29" s="26">
         <f>+L30+L31</f>
-        <v>0</v>
+        <v>2999465</v>
       </c>
       <c r="M29" s="26">
         <f t="shared" ref="M29:S29" si="7">+M30+M31</f>
-        <v>0</v>
+        <v>3039936</v>
       </c>
       <c r="N29" s="26">
         <f t="shared" si="7"/>
@@ -1996,9 +2032,15 @@
       <c r="J30" s="25">
         <v>2936060</v>
       </c>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
+      <c r="K30" s="25">
+        <v>2990674</v>
+      </c>
+      <c r="L30" s="25">
+        <v>2991518</v>
+      </c>
+      <c r="M30" s="25">
+        <v>3032176</v>
+      </c>
       <c r="N30" s="25"/>
       <c r="O30" s="25"/>
       <c r="P30" s="25"/>
@@ -2023,9 +2065,15 @@
       <c r="J31" s="25">
         <v>8049</v>
       </c>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
+      <c r="K31" s="25">
+        <v>8081</v>
+      </c>
+      <c r="L31" s="25">
+        <v>7947</v>
+      </c>
+      <c r="M31" s="25">
+        <v>7760</v>
+      </c>
       <c r="N31" s="25"/>
       <c r="O31" s="25"/>
       <c r="P31" s="25"/>
@@ -2050,9 +2098,15 @@
       <c r="J32" s="22">
         <v>0</v>
       </c>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
+      <c r="K32" s="22">
+        <v>0</v>
+      </c>
+      <c r="L32" s="22">
+        <v>0</v>
+      </c>
+      <c r="M32" s="22">
+        <v>0</v>
+      </c>
       <c r="N32" s="22"/>
       <c r="O32" s="22"/>
       <c r="P32" s="22"/>
@@ -2096,9 +2150,15 @@
       <c r="J34" s="25">
         <v>3009459</v>
       </c>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
+      <c r="K34" s="25">
+        <v>3056450</v>
+      </c>
+      <c r="L34" s="25">
+        <v>3051733</v>
+      </c>
+      <c r="M34" s="25">
+        <v>3187917</v>
+      </c>
       <c r="N34" s="25"/>
       <c r="O34" s="25"/>
       <c r="P34" s="25"/>
@@ -2137,7 +2197,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="32">
         <f>+H38+H42</f>
-        <v>345084</v>
+        <v>345084.65</v>
       </c>
       <c r="I37" s="32">
         <f>+I38+I42</f>
@@ -2149,15 +2209,15 @@
       </c>
       <c r="K37" s="32">
         <f>+K38+K42</f>
-        <v>0</v>
+        <v>383225</v>
       </c>
       <c r="L37" s="32">
         <f>+L38+L42</f>
-        <v>0</v>
+        <v>443502</v>
       </c>
       <c r="M37" s="32">
         <f t="shared" ref="M37:S37" si="8">+M38+M42</f>
-        <v>0</v>
+        <v>305075</v>
       </c>
       <c r="N37" s="32">
         <f t="shared" si="8"/>
@@ -2202,15 +2262,15 @@
       </c>
       <c r="K38" s="34">
         <f>+K39+K40</f>
-        <v>0</v>
+        <v>293217</v>
       </c>
       <c r="L38" s="34">
         <f>+L39+L40</f>
-        <v>0</v>
+        <v>354835</v>
       </c>
       <c r="M38" s="34">
         <f t="shared" ref="M38:S42" si="9">+M39+M40</f>
-        <v>0</v>
+        <v>218134</v>
       </c>
       <c r="N38" s="34">
         <f t="shared" si="9"/>
@@ -2250,9 +2310,15 @@
       <c r="J39" s="35">
         <v>293132</v>
       </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-      <c r="M39" s="35"/>
+      <c r="K39" s="35">
+        <v>293081</v>
+      </c>
+      <c r="L39" s="35">
+        <v>354699</v>
+      </c>
+      <c r="M39" s="35">
+        <v>217998</v>
+      </c>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
       <c r="P39" s="35"/>
@@ -2273,9 +2339,15 @@
       <c r="J40" s="35">
         <v>136</v>
       </c>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
+      <c r="K40" s="35">
+        <v>136</v>
+      </c>
+      <c r="L40" s="35">
+        <v>136</v>
+      </c>
+      <c r="M40" s="35">
+        <v>136</v>
+      </c>
       <c r="N40" s="35"/>
       <c r="O40" s="35"/>
       <c r="P40" s="35"/>
@@ -2306,7 +2378,7 @@
       </c>
       <c r="H42" s="34">
         <f>+H43+H44</f>
-        <v>88353</v>
+        <v>88353.650000000009</v>
       </c>
       <c r="I42" s="34">
         <f>+I43+I44</f>
@@ -2318,15 +2390,15 @@
       </c>
       <c r="K42" s="34">
         <f>+K43+K44</f>
-        <v>0</v>
+        <v>90008</v>
       </c>
       <c r="L42" s="34">
         <f>+L43+L44</f>
-        <v>0</v>
+        <v>88667</v>
       </c>
       <c r="M42" s="34">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>86941</v>
       </c>
       <c r="N42" s="34">
         <f t="shared" si="9"/>
@@ -2358,13 +2430,22 @@
         <v>37</v>
       </c>
       <c r="H43" s="35">
-        <v>83311</v>
+        <v>83311.3</v>
       </c>
       <c r="I43" s="35">
         <v>81023</v>
       </c>
       <c r="J43" s="35">
         <v>82949</v>
+      </c>
+      <c r="K43" s="35">
+        <v>84745</v>
+      </c>
+      <c r="L43" s="35">
+        <v>83408</v>
+      </c>
+      <c r="M43" s="35">
+        <v>81701</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="35" customFormat="1" ht="12.75" customHeight="1">
@@ -2372,13 +2453,22 @@
         <v>38</v>
       </c>
       <c r="H44" s="35">
-        <v>5042</v>
+        <v>5042.3499999999995</v>
       </c>
       <c r="I44" s="35">
         <v>4929</v>
       </c>
       <c r="J44" s="35">
         <v>5189</v>
+      </c>
+      <c r="K44" s="35">
+        <v>5263</v>
+      </c>
+      <c r="L44" s="35">
+        <v>5259</v>
+      </c>
+      <c r="M44" s="35">
+        <v>5240</v>
       </c>
     </row>
     <row r="47" spans="1:19">
